--- a/fixtures/saxo-nl/Transactions_10000000_2025-01-01_2025-12-31.xlsx
+++ b/fixtures/saxo-nl/Transactions_10000000_2025-01-01_2025-12-31.xlsx
@@ -8,13 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="Transacties" sheetId="1" r:id="rId1"/>
+    <sheet name="_Transacties" sheetId="2" r:id="rId2"/>
+    <sheet name="Bookings" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="229">
   <si>
     <t>Klant-id</t>
   </si>
@@ -169,7 +171,7 @@
     <t>40100/9000001EUR</t>
   </si>
   <si>
-    <t>40000001066</t>
+    <t>40000003094</t>
   </si>
   <si>
     <t>Geldoverboeking</t>
@@ -184,13 +186,13 @@
     <t>Cash</t>
   </si>
   <si>
-    <t>40000001053</t>
+    <t>40000003081</t>
   </si>
   <si>
     <t>Saxo Service Fee - October 2025</t>
   </si>
   <si>
-    <t>40000001040</t>
+    <t>40000003042</t>
   </si>
   <si>
     <t>Saxo Service Fee - September 2025</t>
@@ -244,7 +246,7 @@
     <t>5000228</t>
   </si>
   <si>
-    <t>40000001027</t>
+    <t>40000003003</t>
   </si>
   <si>
     <t>Saxo Service Fee - August 2025</t>
@@ -268,7 +270,7 @@
     <t>Euronext Amsterdam</t>
   </si>
   <si>
-    <t>40000001014</t>
+    <t>40000002938</t>
   </si>
   <si>
     <t>Saxo Service Fee - July 2025</t>
@@ -289,7 +291,7 @@
     <t>5000225</t>
   </si>
   <si>
-    <t>40000001001</t>
+    <t>40000002899</t>
   </si>
   <si>
     <t>Saxo Service Fee - June 2025</t>
@@ -319,7 +321,7 @@
     <t>XF0000000095</t>
   </si>
   <si>
-    <t>40000000988</t>
+    <t>40000002808</t>
   </si>
   <si>
     <t>Saxo Service Fee - May 2025</t>
@@ -328,7 +330,7 @@
     <t>5000216</t>
   </si>
   <si>
-    <t>40000000975</t>
+    <t>40000002769</t>
   </si>
   <si>
     <t>Saxo Service Fee - April 2025</t>
@@ -340,7 +342,7 @@
     <t>2500000493</t>
   </si>
   <si>
-    <t>40000000962</t>
+    <t>40000002756</t>
   </si>
   <si>
     <t>Opname</t>
@@ -355,7 +357,7 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t>40000000949</t>
+    <t>40000002717</t>
   </si>
   <si>
     <t>ADR-kosten</t>
@@ -364,7 +366,7 @@
     <t>ADR-kosten XF0000000137</t>
   </si>
   <si>
-    <t>40000000936</t>
+    <t>40000002704</t>
   </si>
   <si>
     <t>Saxo Service Fee - March 2025</t>
@@ -376,13 +378,13 @@
     <t>5000204</t>
   </si>
   <si>
-    <t>40000000923</t>
+    <t>40000002639</t>
   </si>
   <si>
     <t>Saxo Service Fee - February 2025</t>
   </si>
   <si>
-    <t>40000000910</t>
+    <t>40000002626</t>
   </si>
   <si>
     <t>Saxo Service Fee - January 2025</t>
@@ -391,21 +393,325 @@
     <t>5000210</t>
   </si>
   <si>
-    <t>40000000897</t>
+    <t>40000002561</t>
   </si>
   <si>
     <t>Saxo Service Fee - December 2024</t>
   </si>
   <si>
     <t>5000201</t>
+  </si>
+  <si>
+    <t>Order-ID</t>
+  </si>
+  <si>
+    <t>Aangepaste transactiedatum</t>
+  </si>
+  <si>
+    <t>Uitvoeringsdatum transactie</t>
+  </si>
+  <si>
+    <t>Trade Event Type</t>
+  </si>
+  <si>
+    <t>Trade Type</t>
+  </si>
+  <si>
+    <t>Openen/sluiten</t>
+  </si>
+  <si>
+    <t>Traded Quantity</t>
+  </si>
+  <si>
+    <t>Prijs</t>
+  </si>
+  <si>
+    <t>Verhandelde waarde</t>
+  </si>
+  <si>
+    <t>Spreadkosten</t>
+  </si>
+  <si>
+    <t>7000000217</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Verkocht</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Te sluiten</t>
+  </si>
+  <si>
+    <t>7000000224</t>
+  </si>
+  <si>
+    <t>Gekocht</t>
+  </si>
+  <si>
+    <t>Te openen</t>
+  </si>
+  <si>
+    <t>7000000210</t>
+  </si>
+  <si>
+    <t>Amount Type</t>
+  </si>
+  <si>
+    <t>Amount Type Id</t>
+  </si>
+  <si>
+    <t>Boekingsdatum</t>
+  </si>
+  <si>
+    <t>Ex-datum</t>
+  </si>
+  <si>
+    <t>Boekdatum</t>
+  </si>
+  <si>
+    <t>In aanmerking komend aantal</t>
+  </si>
+  <si>
+    <t>Dividend per aandeel</t>
+  </si>
+  <si>
+    <t>Tax Percentage</t>
+  </si>
+  <si>
+    <t>40000003120</t>
+  </si>
+  <si>
+    <t>Corporate Actions - Cashdividenden</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>20-nov-2025</t>
+  </si>
+  <si>
+    <t>16-sep-2025</t>
+  </si>
+  <si>
+    <t>0.86 USD</t>
+  </si>
+  <si>
+    <t>40000003133</t>
+  </si>
+  <si>
+    <t>Corporate actions - Voorheffing</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>40000003107</t>
+  </si>
+  <si>
+    <t>Depository Charges</t>
+  </si>
+  <si>
+    <t>753</t>
+  </si>
+  <si>
+    <t>477</t>
+  </si>
+  <si>
+    <t>40000003068</t>
+  </si>
+  <si>
+    <t>29-aug-2025</t>
+  </si>
+  <si>
+    <t>40000003055</t>
+  </si>
+  <si>
+    <t>0.08 CAD</t>
+  </si>
+  <si>
+    <t>40000003029</t>
+  </si>
+  <si>
+    <t>21-aug-2025</t>
+  </si>
+  <si>
+    <t>11-jun-2025</t>
+  </si>
+  <si>
+    <t>40000003016</t>
+  </si>
+  <si>
+    <t>0.89 USD</t>
+  </si>
+  <si>
+    <t>40000002990</t>
+  </si>
+  <si>
+    <t>04-aug-2025</t>
+  </si>
+  <si>
+    <t>07-feb-2025</t>
+  </si>
+  <si>
+    <t>40000002977</t>
+  </si>
+  <si>
+    <t>Corporate actions - Fracties</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>40000002951</t>
+  </si>
+  <si>
+    <t>25-jul-2025</t>
+  </si>
+  <si>
+    <t>23-jul-2025</t>
+  </si>
+  <si>
+    <t>40000002964</t>
+  </si>
+  <si>
+    <t>40000002925</t>
+  </si>
+  <si>
+    <t>30-mei-2025</t>
+  </si>
+  <si>
+    <t>40000002912</t>
+  </si>
+  <si>
+    <t>40000002873</t>
+  </si>
+  <si>
+    <t>20-jun-2025</t>
+  </si>
+  <si>
+    <t>18-jun-2025</t>
+  </si>
+  <si>
+    <t>40000002886</t>
+  </si>
+  <si>
+    <t>2.17 EUR</t>
+  </si>
+  <si>
+    <t>40000002860</t>
+  </si>
+  <si>
+    <t>15-mei-2025</t>
+  </si>
+  <si>
+    <t>14-mrt-2025</t>
+  </si>
+  <si>
+    <t>40000002847</t>
+  </si>
+  <si>
+    <t>40000002834</t>
+  </si>
+  <si>
+    <t>Corporate Actions - Share Amount</t>
+  </si>
+  <si>
+    <t>338</t>
+  </si>
+  <si>
+    <t>12-mei-2025</t>
+  </si>
+  <si>
+    <t>40000002821</t>
+  </si>
+  <si>
+    <t>40000002782</t>
+  </si>
+  <si>
+    <t>24-apr-2025</t>
+  </si>
+  <si>
+    <t>02-apr-2025</t>
+  </si>
+  <si>
+    <t>40000002795</t>
+  </si>
+  <si>
+    <t>40000002743</t>
+  </si>
+  <si>
+    <t>22-apr-2025</t>
+  </si>
+  <si>
+    <t>30-jan-2025</t>
+  </si>
+  <si>
+    <t>40000002730</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>1000002</t>
+  </si>
+  <si>
+    <t>40000002678</t>
+  </si>
+  <si>
+    <t>28-feb-2025</t>
+  </si>
+  <si>
+    <t>0.07 CAD</t>
+  </si>
+  <si>
+    <t>40000002691</t>
+  </si>
+  <si>
+    <t>40000002652</t>
+  </si>
+  <si>
+    <t>20-feb-2025</t>
+  </si>
+  <si>
+    <t>04-dec-2024</t>
+  </si>
+  <si>
+    <t>40000002665</t>
+  </si>
+  <si>
+    <t>40000002600</t>
+  </si>
+  <si>
+    <t>08-jan-2025</t>
+  </si>
+  <si>
+    <t>40000002613</t>
+  </si>
+  <si>
+    <t>40000002574</t>
+  </si>
+  <si>
+    <t>29-nov-2024</t>
+  </si>
+  <si>
+    <t>40000002587</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy hh:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -436,9 +742,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2837,4 +3144,2848 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:24">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N1" t="s">
+        <v>135</v>
+      </c>
+      <c r="O1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" s="1">
+        <v>45924</v>
+      </c>
+      <c r="I2" s="2">
+        <v>45924.2598726852</v>
+      </c>
+      <c r="J2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L2" t="s">
+        <v>142</v>
+      </c>
+      <c r="M2">
+        <v>-4</v>
+      </c>
+      <c r="N2">
+        <v>87.86</v>
+      </c>
+      <c r="O2">
+        <v>351.44</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U2" t="s">
+        <v>72</v>
+      </c>
+      <c r="V2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" t="s">
+        <v>73</v>
+      </c>
+      <c r="X2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3" s="1">
+        <v>45924</v>
+      </c>
+      <c r="I3" s="2">
+        <v>45924.2598726852</v>
+      </c>
+      <c r="J3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K3" t="s">
+        <v>141</v>
+      </c>
+      <c r="L3" t="s">
+        <v>145</v>
+      </c>
+      <c r="M3">
+        <v>20</v>
+      </c>
+      <c r="N3">
+        <v>18.62</v>
+      </c>
+      <c r="O3">
+        <v>-372.48</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T3" t="s">
+        <v>71</v>
+      </c>
+      <c r="U3" t="s">
+        <v>72</v>
+      </c>
+      <c r="V3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W3" t="s">
+        <v>73</v>
+      </c>
+      <c r="X3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" s="1">
+        <v>45817</v>
+      </c>
+      <c r="I4" s="2">
+        <v>45817.5869444444</v>
+      </c>
+      <c r="J4" t="s">
+        <v>144</v>
+      </c>
+      <c r="K4" t="s">
+        <v>141</v>
+      </c>
+      <c r="L4" t="s">
+        <v>145</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>18.53</v>
+      </c>
+      <c r="O4">
+        <v>-18.53</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" t="s">
+        <v>98</v>
+      </c>
+      <c r="T4" t="s">
+        <v>99</v>
+      </c>
+      <c r="U4" t="s">
+        <v>100</v>
+      </c>
+      <c r="V4" t="s">
+        <v>36</v>
+      </c>
+      <c r="W4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:U46"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:21">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O1" t="s">
+        <v>152</v>
+      </c>
+      <c r="P1" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>154</v>
+      </c>
+      <c r="R1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>3000001595</v>
+      </c>
+      <c r="D2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I2">
+        <v>2.38</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0.770122</v>
+      </c>
+      <c r="L2" s="1">
+        <v>46002</v>
+      </c>
+      <c r="M2" t="s">
+        <v>158</v>
+      </c>
+      <c r="N2" t="s">
+        <v>159</v>
+      </c>
+      <c r="O2">
+        <v>3</v>
+      </c>
+      <c r="P2" t="s">
+        <v>160</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3">
+        <v>3000001595</v>
+      </c>
+      <c r="D3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I3">
+        <v>-0.36</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0.770122</v>
+      </c>
+      <c r="L3" s="1">
+        <v>46002</v>
+      </c>
+      <c r="M3" t="s">
+        <v>158</v>
+      </c>
+      <c r="N3" t="s">
+        <v>159</v>
+      </c>
+      <c r="O3">
+        <v>3</v>
+      </c>
+      <c r="P3" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q3">
+        <v>15</v>
+      </c>
+      <c r="R3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4">
+        <v>3000001584</v>
+      </c>
+      <c r="D4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I4">
+        <v>-0.99</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0.802629</v>
+      </c>
+      <c r="L4" s="1">
+        <v>45996</v>
+      </c>
+      <c r="M4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N4" t="s">
+        <v>164</v>
+      </c>
+      <c r="O4">
+        <v>40</v>
+      </c>
+      <c r="P4" t="s">
+        <v>164</v>
+      </c>
+      <c r="R4" t="s">
+        <v>46</v>
+      </c>
+      <c r="S4" t="s">
+        <v>47</v>
+      </c>
+      <c r="T4" t="s">
+        <v>48</v>
+      </c>
+      <c r="U4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5">
+        <v>3000001573</v>
+      </c>
+      <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" t="s">
+        <v>168</v>
+      </c>
+      <c r="I5">
+        <v>-6.02</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>45992</v>
+      </c>
+      <c r="M5" t="s">
+        <v>164</v>
+      </c>
+      <c r="N5" t="s">
+        <v>164</v>
+      </c>
+      <c r="P5" t="s">
+        <v>164</v>
+      </c>
+      <c r="U5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6">
+        <v>3000001562</v>
+      </c>
+      <c r="D6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" t="s">
+        <v>168</v>
+      </c>
+      <c r="I6">
+        <v>-6.16</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>45964</v>
+      </c>
+      <c r="M6" t="s">
+        <v>164</v>
+      </c>
+      <c r="N6" t="s">
+        <v>164</v>
+      </c>
+      <c r="P6" t="s">
+        <v>164</v>
+      </c>
+      <c r="U6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7">
+        <v>3000001551</v>
+      </c>
+      <c r="D7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" t="s">
+        <v>168</v>
+      </c>
+      <c r="I7">
+        <v>-6.31</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>45931</v>
+      </c>
+      <c r="M7" t="s">
+        <v>164</v>
+      </c>
+      <c r="N7" t="s">
+        <v>164</v>
+      </c>
+      <c r="P7" t="s">
+        <v>164</v>
+      </c>
+      <c r="U7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8">
+        <v>3000001540</v>
+      </c>
+      <c r="D8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>162</v>
+      </c>
+      <c r="H8" t="s">
+        <v>163</v>
+      </c>
+      <c r="I8">
+        <v>-1.86</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0.627447</v>
+      </c>
+      <c r="L8" s="1">
+        <v>45931</v>
+      </c>
+      <c r="M8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N8" t="s">
+        <v>164</v>
+      </c>
+      <c r="O8">
+        <v>199</v>
+      </c>
+      <c r="P8" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q8">
+        <v>25</v>
+      </c>
+      <c r="R8" t="s">
+        <v>63</v>
+      </c>
+      <c r="S8" t="s">
+        <v>64</v>
+      </c>
+      <c r="T8" t="s">
+        <v>65</v>
+      </c>
+      <c r="U8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9">
+        <v>3000001540</v>
+      </c>
+      <c r="D9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>156</v>
+      </c>
+      <c r="H9" t="s">
+        <v>157</v>
+      </c>
+      <c r="I9">
+        <v>7.43</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0.627447</v>
+      </c>
+      <c r="L9" s="1">
+        <v>45931</v>
+      </c>
+      <c r="M9" t="s">
+        <v>170</v>
+      </c>
+      <c r="N9" t="s">
+        <v>164</v>
+      </c>
+      <c r="O9">
+        <v>199</v>
+      </c>
+      <c r="P9" t="s">
+        <v>172</v>
+      </c>
+      <c r="R9" t="s">
+        <v>63</v>
+      </c>
+      <c r="S9" t="s">
+        <v>64</v>
+      </c>
+      <c r="T9" t="s">
+        <v>65</v>
+      </c>
+      <c r="U9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10">
+        <v>3000001529</v>
+      </c>
+      <c r="D10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" t="s">
+        <v>162</v>
+      </c>
+      <c r="H10" t="s">
+        <v>163</v>
+      </c>
+      <c r="I10">
+        <v>-0.31</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.787744</v>
+      </c>
+      <c r="L10" s="1">
+        <v>45911</v>
+      </c>
+      <c r="M10" t="s">
+        <v>174</v>
+      </c>
+      <c r="N10" t="s">
+        <v>175</v>
+      </c>
+      <c r="O10">
+        <v>3</v>
+      </c>
+      <c r="P10" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q10">
+        <v>15</v>
+      </c>
+      <c r="R10" t="s">
+        <v>38</v>
+      </c>
+      <c r="S10" t="s">
+        <v>39</v>
+      </c>
+      <c r="T10" t="s">
+        <v>40</v>
+      </c>
+      <c r="U10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11">
+        <v>3000001529</v>
+      </c>
+      <c r="D11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" t="s">
+        <v>156</v>
+      </c>
+      <c r="H11" t="s">
+        <v>157</v>
+      </c>
+      <c r="I11">
+        <v>2.03</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0.787744</v>
+      </c>
+      <c r="L11" s="1">
+        <v>45911</v>
+      </c>
+      <c r="M11" t="s">
+        <v>174</v>
+      </c>
+      <c r="N11" t="s">
+        <v>175</v>
+      </c>
+      <c r="O11">
+        <v>3</v>
+      </c>
+      <c r="P11" t="s">
+        <v>177</v>
+      </c>
+      <c r="R11" t="s">
+        <v>38</v>
+      </c>
+      <c r="S11" t="s">
+        <v>39</v>
+      </c>
+      <c r="T11" t="s">
+        <v>40</v>
+      </c>
+      <c r="U11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12">
+        <v>3000001518</v>
+      </c>
+      <c r="D12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" t="s">
+        <v>168</v>
+      </c>
+      <c r="I12">
+        <v>-5.63</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>45901</v>
+      </c>
+      <c r="M12" t="s">
+        <v>164</v>
+      </c>
+      <c r="N12" t="s">
+        <v>164</v>
+      </c>
+      <c r="P12" t="s">
+        <v>164</v>
+      </c>
+      <c r="U12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13">
+        <v>3000001507</v>
+      </c>
+      <c r="D13" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" t="s">
+        <v>162</v>
+      </c>
+      <c r="H13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I13">
+        <v>-0.14</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>45880</v>
+      </c>
+      <c r="M13" t="s">
+        <v>179</v>
+      </c>
+      <c r="N13" t="s">
+        <v>180</v>
+      </c>
+      <c r="O13">
+        <v>3</v>
+      </c>
+      <c r="P13" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q13">
+        <v>15</v>
+      </c>
+      <c r="R13" t="s">
+        <v>80</v>
+      </c>
+      <c r="S13" t="s">
+        <v>81</v>
+      </c>
+      <c r="T13" t="s">
+        <v>82</v>
+      </c>
+      <c r="U13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14">
+        <v>3000001507</v>
+      </c>
+      <c r="D14" t="s">
+        <v>181</v>
+      </c>
+      <c r="E14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" t="s">
+        <v>182</v>
+      </c>
+      <c r="H14" t="s">
+        <v>183</v>
+      </c>
+      <c r="I14">
+        <v>0.94</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
+        <v>45880</v>
+      </c>
+      <c r="M14" t="s">
+        <v>179</v>
+      </c>
+      <c r="N14" t="s">
+        <v>180</v>
+      </c>
+      <c r="O14">
+        <v>3</v>
+      </c>
+      <c r="P14" t="s">
+        <v>164</v>
+      </c>
+      <c r="R14" t="s">
+        <v>80</v>
+      </c>
+      <c r="S14" t="s">
+        <v>81</v>
+      </c>
+      <c r="T14" t="s">
+        <v>82</v>
+      </c>
+      <c r="U14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15">
+        <v>3000001496</v>
+      </c>
+      <c r="D15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" t="s">
+        <v>168</v>
+      </c>
+      <c r="I15">
+        <v>-5.69</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>45870</v>
+      </c>
+      <c r="M15" t="s">
+        <v>164</v>
+      </c>
+      <c r="N15" t="s">
+        <v>164</v>
+      </c>
+      <c r="P15" t="s">
+        <v>164</v>
+      </c>
+      <c r="U15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16">
+        <v>3000001485</v>
+      </c>
+      <c r="D16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" t="s">
+        <v>162</v>
+      </c>
+      <c r="H16" t="s">
+        <v>163</v>
+      </c>
+      <c r="I16">
+        <v>-0.05</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1">
+        <v>45870</v>
+      </c>
+      <c r="M16" t="s">
+        <v>185</v>
+      </c>
+      <c r="N16" t="s">
+        <v>186</v>
+      </c>
+      <c r="O16">
+        <v>3</v>
+      </c>
+      <c r="P16" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q16">
+        <v>15</v>
+      </c>
+      <c r="R16" t="s">
+        <v>87</v>
+      </c>
+      <c r="S16" t="s">
+        <v>88</v>
+      </c>
+      <c r="T16" t="s">
+        <v>89</v>
+      </c>
+      <c r="U16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17">
+        <v>3000001485</v>
+      </c>
+      <c r="D17" t="s">
+        <v>187</v>
+      </c>
+      <c r="E17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" t="s">
+        <v>182</v>
+      </c>
+      <c r="H17" t="s">
+        <v>183</v>
+      </c>
+      <c r="I17">
+        <v>0.23</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>45870</v>
+      </c>
+      <c r="M17" t="s">
+        <v>185</v>
+      </c>
+      <c r="N17" t="s">
+        <v>186</v>
+      </c>
+      <c r="O17">
+        <v>3</v>
+      </c>
+      <c r="P17" t="s">
+        <v>164</v>
+      </c>
+      <c r="R17" t="s">
+        <v>87</v>
+      </c>
+      <c r="S17" t="s">
+        <v>88</v>
+      </c>
+      <c r="T17" t="s">
+        <v>89</v>
+      </c>
+      <c r="U17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18">
+        <v>3000001474</v>
+      </c>
+      <c r="D18" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" t="s">
+        <v>162</v>
+      </c>
+      <c r="H18" t="s">
+        <v>163</v>
+      </c>
+      <c r="I18">
+        <v>-2.14</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0.674184</v>
+      </c>
+      <c r="L18" s="1">
+        <v>45840</v>
+      </c>
+      <c r="M18" t="s">
+        <v>189</v>
+      </c>
+      <c r="N18" t="s">
+        <v>164</v>
+      </c>
+      <c r="O18">
+        <v>199</v>
+      </c>
+      <c r="P18" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q18">
+        <v>25</v>
+      </c>
+      <c r="R18" t="s">
+        <v>63</v>
+      </c>
+      <c r="S18" t="s">
+        <v>64</v>
+      </c>
+      <c r="T18" t="s">
+        <v>65</v>
+      </c>
+      <c r="U18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19">
+        <v>3000001474</v>
+      </c>
+      <c r="D19" t="s">
+        <v>190</v>
+      </c>
+      <c r="E19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" t="s">
+        <v>156</v>
+      </c>
+      <c r="H19" t="s">
+        <v>157</v>
+      </c>
+      <c r="I19">
+        <v>8.54</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0.674184</v>
+      </c>
+      <c r="L19" s="1">
+        <v>45840</v>
+      </c>
+      <c r="M19" t="s">
+        <v>189</v>
+      </c>
+      <c r="N19" t="s">
+        <v>164</v>
+      </c>
+      <c r="O19">
+        <v>199</v>
+      </c>
+      <c r="P19" t="s">
+        <v>172</v>
+      </c>
+      <c r="R19" t="s">
+        <v>63</v>
+      </c>
+      <c r="S19" t="s">
+        <v>64</v>
+      </c>
+      <c r="T19" t="s">
+        <v>65</v>
+      </c>
+      <c r="U19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20">
+        <v>3000001463</v>
+      </c>
+      <c r="D20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" t="s">
+        <v>168</v>
+      </c>
+      <c r="I20">
+        <v>-5.58</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>45839</v>
+      </c>
+      <c r="M20" t="s">
+        <v>164</v>
+      </c>
+      <c r="N20" t="s">
+        <v>164</v>
+      </c>
+      <c r="P20" t="s">
+        <v>164</v>
+      </c>
+      <c r="U20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21">
+        <v>3000001452</v>
+      </c>
+      <c r="D21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E21" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" t="s">
+        <v>162</v>
+      </c>
+      <c r="H21" t="s">
+        <v>163</v>
+      </c>
+      <c r="I21">
+        <v>-1.34</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1">
+        <v>45838</v>
+      </c>
+      <c r="M21" t="s">
+        <v>192</v>
+      </c>
+      <c r="N21" t="s">
+        <v>193</v>
+      </c>
+      <c r="O21">
+        <v>4</v>
+      </c>
+      <c r="P21" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q21">
+        <v>15</v>
+      </c>
+      <c r="R21" t="s">
+        <v>70</v>
+      </c>
+      <c r="S21" t="s">
+        <v>71</v>
+      </c>
+      <c r="T21" t="s">
+        <v>72</v>
+      </c>
+      <c r="U21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22">
+        <v>3000001452</v>
+      </c>
+      <c r="D22" t="s">
+        <v>194</v>
+      </c>
+      <c r="E22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" t="s">
+        <v>156</v>
+      </c>
+      <c r="H22" t="s">
+        <v>157</v>
+      </c>
+      <c r="I22">
+        <v>8.93</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>45838</v>
+      </c>
+      <c r="M22" t="s">
+        <v>192</v>
+      </c>
+      <c r="N22" t="s">
+        <v>193</v>
+      </c>
+      <c r="O22">
+        <v>4</v>
+      </c>
+      <c r="P22" t="s">
+        <v>195</v>
+      </c>
+      <c r="R22" t="s">
+        <v>70</v>
+      </c>
+      <c r="S22" t="s">
+        <v>71</v>
+      </c>
+      <c r="T22" t="s">
+        <v>72</v>
+      </c>
+      <c r="U22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23">
+        <v>3000001441</v>
+      </c>
+      <c r="D23" t="s">
+        <v>196</v>
+      </c>
+      <c r="E23" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" t="s">
+        <v>162</v>
+      </c>
+      <c r="H23" t="s">
+        <v>163</v>
+      </c>
+      <c r="I23">
+        <v>-0.35</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0.906143</v>
+      </c>
+      <c r="L23" s="1">
+        <v>45820</v>
+      </c>
+      <c r="M23" t="s">
+        <v>197</v>
+      </c>
+      <c r="N23" t="s">
+        <v>198</v>
+      </c>
+      <c r="O23">
+        <v>3</v>
+      </c>
+      <c r="P23" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q23">
+        <v>15</v>
+      </c>
+      <c r="R23" t="s">
+        <v>38</v>
+      </c>
+      <c r="S23" t="s">
+        <v>39</v>
+      </c>
+      <c r="T23" t="s">
+        <v>40</v>
+      </c>
+      <c r="U23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24">
+        <v>3000001441</v>
+      </c>
+      <c r="D24" t="s">
+        <v>199</v>
+      </c>
+      <c r="E24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" t="s">
+        <v>156</v>
+      </c>
+      <c r="H24" t="s">
+        <v>157</v>
+      </c>
+      <c r="I24">
+        <v>2.35</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0.906143</v>
+      </c>
+      <c r="L24" s="1">
+        <v>45820</v>
+      </c>
+      <c r="M24" t="s">
+        <v>197</v>
+      </c>
+      <c r="N24" t="s">
+        <v>198</v>
+      </c>
+      <c r="O24">
+        <v>3</v>
+      </c>
+      <c r="P24" t="s">
+        <v>177</v>
+      </c>
+      <c r="R24" t="s">
+        <v>38</v>
+      </c>
+      <c r="S24" t="s">
+        <v>39</v>
+      </c>
+      <c r="T24" t="s">
+        <v>40</v>
+      </c>
+      <c r="U24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" t="s">
+        <v>200</v>
+      </c>
+      <c r="E25" t="s">
+        <v>96</v>
+      </c>
+      <c r="F25" t="s">
+        <v>97</v>
+      </c>
+      <c r="G25" t="s">
+        <v>201</v>
+      </c>
+      <c r="H25" t="s">
+        <v>202</v>
+      </c>
+      <c r="I25">
+        <v>-20.92</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1">
+        <v>45817</v>
+      </c>
+      <c r="M25" t="s">
+        <v>203</v>
+      </c>
+      <c r="N25" t="s">
+        <v>164</v>
+      </c>
+      <c r="O25">
+        <v>33</v>
+      </c>
+      <c r="P25" t="s">
+        <v>164</v>
+      </c>
+      <c r="R25" t="s">
+        <v>98</v>
+      </c>
+      <c r="S25" t="s">
+        <v>99</v>
+      </c>
+      <c r="T25" t="s">
+        <v>100</v>
+      </c>
+      <c r="U25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" t="s">
+        <v>204</v>
+      </c>
+      <c r="E26" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" t="s">
+        <v>97</v>
+      </c>
+      <c r="G26" t="s">
+        <v>156</v>
+      </c>
+      <c r="H26" t="s">
+        <v>157</v>
+      </c>
+      <c r="I26">
+        <v>29.21</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1">
+        <v>45817</v>
+      </c>
+      <c r="M26" t="s">
+        <v>203</v>
+      </c>
+      <c r="N26" t="s">
+        <v>164</v>
+      </c>
+      <c r="O26">
+        <v>33</v>
+      </c>
+      <c r="P26" t="s">
+        <v>164</v>
+      </c>
+      <c r="R26" t="s">
+        <v>98</v>
+      </c>
+      <c r="S26" t="s">
+        <v>99</v>
+      </c>
+      <c r="T26" t="s">
+        <v>100</v>
+      </c>
+      <c r="U26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27">
+        <v>3000001430</v>
+      </c>
+      <c r="D27" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" t="s">
+        <v>168</v>
+      </c>
+      <c r="I27">
+        <v>-5.6</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <v>45810</v>
+      </c>
+      <c r="M27" t="s">
+        <v>164</v>
+      </c>
+      <c r="N27" t="s">
+        <v>164</v>
+      </c>
+      <c r="P27" t="s">
+        <v>164</v>
+      </c>
+      <c r="U27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28">
+        <v>3000001419</v>
+      </c>
+      <c r="D28" t="s">
+        <v>205</v>
+      </c>
+      <c r="E28" t="s">
+        <v>103</v>
+      </c>
+      <c r="F28" t="s">
+        <v>79</v>
+      </c>
+      <c r="G28" t="s">
+        <v>162</v>
+      </c>
+      <c r="H28" t="s">
+        <v>163</v>
+      </c>
+      <c r="I28">
+        <v>-0.33</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
+        <v>45779</v>
+      </c>
+      <c r="M28" t="s">
+        <v>206</v>
+      </c>
+      <c r="N28" t="s">
+        <v>207</v>
+      </c>
+      <c r="O28">
+        <v>3</v>
+      </c>
+      <c r="P28" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q28">
+        <v>15</v>
+      </c>
+      <c r="R28" t="s">
+        <v>80</v>
+      </c>
+      <c r="S28" t="s">
+        <v>81</v>
+      </c>
+      <c r="T28" t="s">
+        <v>82</v>
+      </c>
+      <c r="U28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="A29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29">
+        <v>3000001419</v>
+      </c>
+      <c r="D29" t="s">
+        <v>208</v>
+      </c>
+      <c r="E29" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29" t="s">
+        <v>79</v>
+      </c>
+      <c r="G29" t="s">
+        <v>182</v>
+      </c>
+      <c r="H29" t="s">
+        <v>183</v>
+      </c>
+      <c r="I29">
+        <v>2.22</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1">
+        <v>45779</v>
+      </c>
+      <c r="M29" t="s">
+        <v>206</v>
+      </c>
+      <c r="N29" t="s">
+        <v>207</v>
+      </c>
+      <c r="O29">
+        <v>3</v>
+      </c>
+      <c r="P29" t="s">
+        <v>164</v>
+      </c>
+      <c r="R29" t="s">
+        <v>80</v>
+      </c>
+      <c r="S29" t="s">
+        <v>81</v>
+      </c>
+      <c r="T29" t="s">
+        <v>82</v>
+      </c>
+      <c r="U29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="A30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30">
+        <v>3000001408</v>
+      </c>
+      <c r="D30" t="s">
+        <v>104</v>
+      </c>
+      <c r="F30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" t="s">
+        <v>168</v>
+      </c>
+      <c r="I30">
+        <v>-4.7</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1">
+        <v>45778</v>
+      </c>
+      <c r="M30" t="s">
+        <v>164</v>
+      </c>
+      <c r="N30" t="s">
+        <v>164</v>
+      </c>
+      <c r="P30" t="s">
+        <v>164</v>
+      </c>
+      <c r="U30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="A31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31">
+        <v>3000001397</v>
+      </c>
+      <c r="D31" t="s">
+        <v>209</v>
+      </c>
+      <c r="E31" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" t="s">
+        <v>79</v>
+      </c>
+      <c r="G31" t="s">
+        <v>162</v>
+      </c>
+      <c r="H31" t="s">
+        <v>163</v>
+      </c>
+      <c r="I31">
+        <v>-0.06</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1">
+        <v>45775</v>
+      </c>
+      <c r="M31" t="s">
+        <v>210</v>
+      </c>
+      <c r="N31" t="s">
+        <v>211</v>
+      </c>
+      <c r="O31">
+        <v>3</v>
+      </c>
+      <c r="P31" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q31">
+        <v>15</v>
+      </c>
+      <c r="R31" t="s">
+        <v>87</v>
+      </c>
+      <c r="S31" t="s">
+        <v>88</v>
+      </c>
+      <c r="T31" t="s">
+        <v>89</v>
+      </c>
+      <c r="U31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32">
+        <v>3000001397</v>
+      </c>
+      <c r="D32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E32" t="s">
+        <v>106</v>
+      </c>
+      <c r="F32" t="s">
+        <v>79</v>
+      </c>
+      <c r="G32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I32">
+        <v>0.34</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1">
+        <v>45775</v>
+      </c>
+      <c r="M32" t="s">
+        <v>210</v>
+      </c>
+      <c r="N32" t="s">
+        <v>211</v>
+      </c>
+      <c r="O32">
+        <v>3</v>
+      </c>
+      <c r="P32" t="s">
+        <v>164</v>
+      </c>
+      <c r="R32" t="s">
+        <v>87</v>
+      </c>
+      <c r="S32" t="s">
+        <v>88</v>
+      </c>
+      <c r="T32" t="s">
+        <v>89</v>
+      </c>
+      <c r="U32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
+      <c r="A33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33">
+        <v>3000001386</v>
+      </c>
+      <c r="D33" t="s">
+        <v>108</v>
+      </c>
+      <c r="F33" t="s">
+        <v>109</v>
+      </c>
+      <c r="G33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" t="s">
+        <v>213</v>
+      </c>
+      <c r="I33">
+        <v>-9814</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1">
+        <v>45775</v>
+      </c>
+      <c r="M33" t="s">
+        <v>164</v>
+      </c>
+      <c r="N33" t="s">
+        <v>164</v>
+      </c>
+      <c r="P33" t="s">
+        <v>164</v>
+      </c>
+      <c r="U33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34">
+        <v>3000001375</v>
+      </c>
+      <c r="D34" t="s">
+        <v>113</v>
+      </c>
+      <c r="F34" t="s">
+        <v>114</v>
+      </c>
+      <c r="G34" t="s">
+        <v>114</v>
+      </c>
+      <c r="H34" t="s">
+        <v>214</v>
+      </c>
+      <c r="I34">
+        <v>-0.67</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0.908869</v>
+      </c>
+      <c r="L34" s="1">
+        <v>45750</v>
+      </c>
+      <c r="M34" t="s">
+        <v>164</v>
+      </c>
+      <c r="N34" t="s">
+        <v>164</v>
+      </c>
+      <c r="P34" t="s">
+        <v>164</v>
+      </c>
+      <c r="R34" t="s">
+        <v>46</v>
+      </c>
+      <c r="S34" t="s">
+        <v>47</v>
+      </c>
+      <c r="T34" t="s">
+        <v>48</v>
+      </c>
+      <c r="U34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
+      <c r="A35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35">
+        <v>3000001364</v>
+      </c>
+      <c r="D35" t="s">
+        <v>116</v>
+      </c>
+      <c r="F35" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35" t="s">
+        <v>53</v>
+      </c>
+      <c r="H35" t="s">
+        <v>168</v>
+      </c>
+      <c r="I35">
+        <v>-4.87</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1">
+        <v>45748</v>
+      </c>
+      <c r="M35" t="s">
+        <v>164</v>
+      </c>
+      <c r="N35" t="s">
+        <v>164</v>
+      </c>
+      <c r="P35" t="s">
+        <v>164</v>
+      </c>
+      <c r="U35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
+      <c r="A36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36">
+        <v>3000001353</v>
+      </c>
+      <c r="D36" t="s">
+        <v>215</v>
+      </c>
+      <c r="E36" t="s">
+        <v>118</v>
+      </c>
+      <c r="F36" t="s">
+        <v>35</v>
+      </c>
+      <c r="G36" t="s">
+        <v>156</v>
+      </c>
+      <c r="H36" t="s">
+        <v>157</v>
+      </c>
+      <c r="I36">
+        <v>8.24</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0.605688</v>
+      </c>
+      <c r="L36" s="1">
+        <v>45748</v>
+      </c>
+      <c r="M36" t="s">
+        <v>216</v>
+      </c>
+      <c r="N36" t="s">
+        <v>164</v>
+      </c>
+      <c r="O36">
+        <v>199</v>
+      </c>
+      <c r="P36" t="s">
+        <v>217</v>
+      </c>
+      <c r="R36" t="s">
+        <v>63</v>
+      </c>
+      <c r="S36" t="s">
+        <v>64</v>
+      </c>
+      <c r="T36" t="s">
+        <v>65</v>
+      </c>
+      <c r="U36" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37">
+        <v>3000001353</v>
+      </c>
+      <c r="D37" t="s">
+        <v>218</v>
+      </c>
+      <c r="E37" t="s">
+        <v>118</v>
+      </c>
+      <c r="F37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" t="s">
+        <v>162</v>
+      </c>
+      <c r="H37" t="s">
+        <v>163</v>
+      </c>
+      <c r="I37">
+        <v>-1.98</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0.605688</v>
+      </c>
+      <c r="L37" s="1">
+        <v>45748</v>
+      </c>
+      <c r="M37" t="s">
+        <v>216</v>
+      </c>
+      <c r="N37" t="s">
+        <v>164</v>
+      </c>
+      <c r="O37">
+        <v>199</v>
+      </c>
+      <c r="P37" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q37">
+        <v>25</v>
+      </c>
+      <c r="R37" t="s">
+        <v>63</v>
+      </c>
+      <c r="S37" t="s">
+        <v>64</v>
+      </c>
+      <c r="T37" t="s">
+        <v>65</v>
+      </c>
+      <c r="U37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
+      <c r="A38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38">
+        <v>3000001342</v>
+      </c>
+      <c r="D38" t="s">
+        <v>219</v>
+      </c>
+      <c r="E38" t="s">
+        <v>119</v>
+      </c>
+      <c r="F38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G38" t="s">
+        <v>156</v>
+      </c>
+      <c r="H38" t="s">
+        <v>157</v>
+      </c>
+      <c r="I38">
+        <v>2.2</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0.900518</v>
+      </c>
+      <c r="L38" s="1">
+        <v>45729</v>
+      </c>
+      <c r="M38" t="s">
+        <v>220</v>
+      </c>
+      <c r="N38" t="s">
+        <v>221</v>
+      </c>
+      <c r="O38">
+        <v>3</v>
+      </c>
+      <c r="P38" t="s">
+        <v>177</v>
+      </c>
+      <c r="R38" t="s">
+        <v>38</v>
+      </c>
+      <c r="S38" t="s">
+        <v>39</v>
+      </c>
+      <c r="T38" t="s">
+        <v>40</v>
+      </c>
+      <c r="U38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
+      <c r="A39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39">
+        <v>3000001342</v>
+      </c>
+      <c r="D39" t="s">
+        <v>222</v>
+      </c>
+      <c r="E39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F39" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" t="s">
+        <v>162</v>
+      </c>
+      <c r="H39" t="s">
+        <v>163</v>
+      </c>
+      <c r="I39">
+        <v>-0.33</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0.900518</v>
+      </c>
+      <c r="L39" s="1">
+        <v>45729</v>
+      </c>
+      <c r="M39" t="s">
+        <v>220</v>
+      </c>
+      <c r="N39" t="s">
+        <v>221</v>
+      </c>
+      <c r="O39">
+        <v>3</v>
+      </c>
+      <c r="P39" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q39">
+        <v>15</v>
+      </c>
+      <c r="R39" t="s">
+        <v>38</v>
+      </c>
+      <c r="S39" t="s">
+        <v>39</v>
+      </c>
+      <c r="T39" t="s">
+        <v>40</v>
+      </c>
+      <c r="U39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40">
+        <v>3000001331</v>
+      </c>
+      <c r="D40" t="s">
+        <v>120</v>
+      </c>
+      <c r="F40" t="s">
+        <v>53</v>
+      </c>
+      <c r="G40" t="s">
+        <v>53</v>
+      </c>
+      <c r="H40" t="s">
+        <v>168</v>
+      </c>
+      <c r="I40">
+        <v>-5.43</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40" s="1">
+        <v>45719</v>
+      </c>
+      <c r="M40" t="s">
+        <v>164</v>
+      </c>
+      <c r="N40" t="s">
+        <v>164</v>
+      </c>
+      <c r="P40" t="s">
+        <v>164</v>
+      </c>
+      <c r="U40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41">
+        <v>3000001320</v>
+      </c>
+      <c r="D41" t="s">
+        <v>122</v>
+      </c>
+      <c r="F41" t="s">
+        <v>53</v>
+      </c>
+      <c r="G41" t="s">
+        <v>53</v>
+      </c>
+      <c r="H41" t="s">
+        <v>168</v>
+      </c>
+      <c r="I41">
+        <v>-5.99</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41" s="1">
+        <v>45691</v>
+      </c>
+      <c r="M41" t="s">
+        <v>164</v>
+      </c>
+      <c r="N41" t="s">
+        <v>164</v>
+      </c>
+      <c r="P41" t="s">
+        <v>164</v>
+      </c>
+      <c r="U41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
+      <c r="A42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42">
+        <v>3000001309</v>
+      </c>
+      <c r="D42" t="s">
+        <v>223</v>
+      </c>
+      <c r="E42" t="s">
+        <v>124</v>
+      </c>
+      <c r="F42" t="s">
+        <v>79</v>
+      </c>
+      <c r="G42" t="s">
+        <v>182</v>
+      </c>
+      <c r="H42" t="s">
+        <v>183</v>
+      </c>
+      <c r="I42">
+        <v>0.47</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1">
+        <v>45673</v>
+      </c>
+      <c r="M42" t="s">
+        <v>224</v>
+      </c>
+      <c r="N42" t="s">
+        <v>164</v>
+      </c>
+      <c r="O42">
+        <v>3</v>
+      </c>
+      <c r="P42" t="s">
+        <v>164</v>
+      </c>
+      <c r="R42" t="s">
+        <v>80</v>
+      </c>
+      <c r="S42" t="s">
+        <v>81</v>
+      </c>
+      <c r="T42" t="s">
+        <v>82</v>
+      </c>
+      <c r="U42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
+      <c r="A43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43">
+        <v>3000001309</v>
+      </c>
+      <c r="D43" t="s">
+        <v>225</v>
+      </c>
+      <c r="E43" t="s">
+        <v>124</v>
+      </c>
+      <c r="F43" t="s">
+        <v>79</v>
+      </c>
+      <c r="G43" t="s">
+        <v>162</v>
+      </c>
+      <c r="H43" t="s">
+        <v>163</v>
+      </c>
+      <c r="I43">
+        <v>-0.08</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1">
+        <v>45673</v>
+      </c>
+      <c r="M43" t="s">
+        <v>224</v>
+      </c>
+      <c r="N43" t="s">
+        <v>164</v>
+      </c>
+      <c r="O43">
+        <v>3</v>
+      </c>
+      <c r="P43" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q43">
+        <v>15</v>
+      </c>
+      <c r="R43" t="s">
+        <v>80</v>
+      </c>
+      <c r="S43" t="s">
+        <v>81</v>
+      </c>
+      <c r="T43" t="s">
+        <v>82</v>
+      </c>
+      <c r="U43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
+      <c r="A44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44">
+        <v>3000001298</v>
+      </c>
+      <c r="D44" t="s">
+        <v>125</v>
+      </c>
+      <c r="F44" t="s">
+        <v>53</v>
+      </c>
+      <c r="G44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H44" t="s">
+        <v>168</v>
+      </c>
+      <c r="I44">
+        <v>-6.08</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="L44" s="1">
+        <v>45659</v>
+      </c>
+      <c r="M44" t="s">
+        <v>164</v>
+      </c>
+      <c r="N44" t="s">
+        <v>164</v>
+      </c>
+      <c r="P44" t="s">
+        <v>164</v>
+      </c>
+      <c r="U44" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
+      <c r="A45" t="s">
+        <v>60</v>
+      </c>
+      <c r="C45">
+        <v>3000001287</v>
+      </c>
+      <c r="D45" t="s">
+        <v>226</v>
+      </c>
+      <c r="E45" t="s">
+        <v>127</v>
+      </c>
+      <c r="F45" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" t="s">
+        <v>156</v>
+      </c>
+      <c r="H45" t="s">
+        <v>157</v>
+      </c>
+      <c r="I45">
+        <v>8.54</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0.692654</v>
+      </c>
+      <c r="L45" s="1">
+        <v>45659</v>
+      </c>
+      <c r="M45" t="s">
+        <v>227</v>
+      </c>
+      <c r="N45" t="s">
+        <v>164</v>
+      </c>
+      <c r="O45">
+        <v>199</v>
+      </c>
+      <c r="P45" t="s">
+        <v>217</v>
+      </c>
+      <c r="R45" t="s">
+        <v>63</v>
+      </c>
+      <c r="S45" t="s">
+        <v>64</v>
+      </c>
+      <c r="T45" t="s">
+        <v>65</v>
+      </c>
+      <c r="U45" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
+      <c r="A46" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46">
+        <v>3000001287</v>
+      </c>
+      <c r="D46" t="s">
+        <v>228</v>
+      </c>
+      <c r="E46" t="s">
+        <v>127</v>
+      </c>
+      <c r="F46" t="s">
+        <v>35</v>
+      </c>
+      <c r="G46" t="s">
+        <v>162</v>
+      </c>
+      <c r="H46" t="s">
+        <v>163</v>
+      </c>
+      <c r="I46">
+        <v>-2.14</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0.692654</v>
+      </c>
+      <c r="L46" s="1">
+        <v>45659</v>
+      </c>
+      <c r="M46" t="s">
+        <v>227</v>
+      </c>
+      <c r="N46" t="s">
+        <v>164</v>
+      </c>
+      <c r="O46">
+        <v>199</v>
+      </c>
+      <c r="P46" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q46">
+        <v>25</v>
+      </c>
+      <c r="R46" t="s">
+        <v>63</v>
+      </c>
+      <c r="S46" t="s">
+        <v>64</v>
+      </c>
+      <c r="T46" t="s">
+        <v>65</v>
+      </c>
+      <c r="U46" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>